--- a/Scenario_3/XLSX Files/Scenario_3/Scenario_3_NOVS.xlsx
+++ b/Scenario_3/XLSX Files/Scenario_3/Scenario_3_NOVS.xlsx
@@ -438,7 +438,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8125</v>
+        <v>0.925</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -579,13 +579,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.825</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0625</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.7375</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -624,13 +624,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.75</v>
+        <v>0.475</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -639,13 +639,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.075</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -654,13 +654,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.35</v>
+        <v>0.425</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.3875</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -684,13 +684,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ea.p.n.Small-3</t>
+          <t>ea.p.n.Large-5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ea.p.n.Small-3</t>
+          <t>ea.p.n.Large-5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.675</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ea.p.n.Small-3</t>
+          <t>ea.p.n.Large-5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ea.p.n.Small-3</t>
+          <t>ea.p.n.Large-5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -744,13 +744,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.725</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ea.p.n.Small-3</t>
+          <t>ea.p.n.Large-5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.825</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ea.p.n.Small-3</t>
+          <t>ea.p.n.Large-5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0375</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ea.p.n.Small-3</t>
+          <t>ea.p.n.Large-5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.3875</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ea.p.n.Small-3</t>
+          <t>ea.p.n.Large-5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -804,22 +804,967 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.4875</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>ea.p.n.Large-5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>cmaEs</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>differentialEvolution</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>es-0.02</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>es-0.25</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>es-0.5</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ga-0.02</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ga-0.25</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ga-0.5</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.675</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>cmaEs</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>differentialEvolution</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.825</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>es-0.02</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>es-0.25</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.175</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>es-0.5</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.175</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ga-0.02</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ga-0.25</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ga-0.5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.425</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>cmaEs</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>differentialEvolution</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>es-0.02</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>es-0.25</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>es-0.5</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.325</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ga-0.02</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ga-0.25</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.725</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ga-0.5</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.525</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>cmaEs</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>differentialEvolution</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>es-0.02</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>es-0.25</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>es-0.5</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ga-0.02</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.575</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ga-0.25</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.675</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ga-0.5</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>ea.p.n.Small-3</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>cmaEs</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>differentialEvolution</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>es-0.02</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-3</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>es-0.25</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-3</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>es-0.5</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-3</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ga-0.02</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-3</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ga-0.25</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-3</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ga-0.5</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-3</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>pso</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>0.5625</v>
+      <c r="C64" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>cmaEs</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>differentialEvolution</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>es-0.02</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.475</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>es-0.25</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>es-0.5</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.525</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ga-0.02</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ga-0.25</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ga-0.5</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>cmaEs</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>differentialEvolution</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.475</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>es-0.02</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.525</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>es-0.25</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>es-0.5</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.425</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ga-0.02</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.675</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ga-0.25</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ga-0.5</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0.425</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0.825</v>
       </c>
     </row>
   </sheetData>
@@ -833,7 +1778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,7 +1801,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -865,13 +1810,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -880,13 +1825,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>637.5</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -894,12 +1839,14 @@
           <t>es-0.02</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>2480</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -908,13 +1855,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>900</v>
+        <v>1342.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,13 +1870,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>855</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -938,13 +1885,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1850</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -953,13 +1900,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1850</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -968,13 +1915,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -983,13 +1930,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>950</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ea.p.n.Small-3</t>
+          <t>ea.p.n.Large-5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -998,13 +1945,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1158.75</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ea.p.n.Small-3</t>
+          <t>ea.p.n.Large-5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1013,13 +1960,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>802.5</v>
+        <v>1102.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ea.p.n.Small-3</t>
+          <t>ea.p.n.Large-5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1027,12 +1974,14 @@
           <t>es-0.02</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>2280</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ea.p.n.Small-3</t>
+          <t>ea.p.n.Large-5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1041,13 +1990,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1480</v>
+        <v>1342.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ea.p.n.Small-3</t>
+          <t>ea.p.n.Large-5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1056,13 +2005,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1020</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ea.p.n.Small-3</t>
+          <t>ea.p.n.Large-5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1070,12 +2019,14 @@
           <t>ga-0.02</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>2100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ea.p.n.Small-3</t>
+          <t>ea.p.n.Large-5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1084,13 +2035,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2044.444444444444</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ea.p.n.Small-3</t>
+          <t>ea.p.n.Large-5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1099,22 +2050,967 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1544.444444444444</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>ea.p.n.Large-5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>cmaEs</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1173.333333333333</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>differentialEvolution</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>es-0.02</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>es-0.25</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>es-0.5</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ga-0.02</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ga-0.25</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ga-0.5</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>cmaEs</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1102.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>differentialEvolution</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>es-0.02</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>es-0.25</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>es-0.5</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ga-0.02</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ga-0.25</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ga-0.5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>cmaEs</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>differentialEvolution</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>es-0.02</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>es-0.25</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>es-0.5</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ga-0.02</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ga-0.25</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ga-0.5</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>cmaEs</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>522.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>differentialEvolution</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>es-0.02</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>es-0.25</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1042.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>es-0.5</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1042.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ga-0.02</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ga-0.25</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ga-0.5</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>ea.p.n.Small-3</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>cmaEs</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>differentialEvolution</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>es-0.02</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-3</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>es-0.25</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-3</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>es-0.5</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-3</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ga-0.02</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-3</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ga-0.25</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-3</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ga-0.5</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-3</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>pso</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>1155.555555555556</v>
+      <c r="C64" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>cmaEs</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>differentialEvolution</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>es-0.02</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>es-0.25</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>es-0.5</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ga-0.02</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ga-0.25</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ga-0.5</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>cmaEs</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>differentialEvolution</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>es-0.02</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>es-0.25</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>es-0.5</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ga-0.02</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ga-0.25</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ga-0.5</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>pso</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -1128,15 +3024,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>problem</t>
-        </is>
-      </c>
       <c r="B1" t="inlineStr">
         <is>
           <t>cmaEs</t>
@@ -1186,69 +3077,307 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ea.p.n.Maze-3</t>
+          <t>ea.p.n.Large-3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>ea.p.n.Large-5</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ea.p.n.Large-9</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-3</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ea.p.n.Maze-9</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>ea.p.n.Small-3</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-5</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ea.p.n.Small-9</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
